--- a/Supporting Materials/poker_ranges_cash_gto.xlsx
+++ b/Supporting Materials/poker_ranges_cash_gto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/greg/Library/CloudStorage/Dropbox/Personal/Python/GTO/Supporting Materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDC0F46-57E0-8541-BA68-46E9F8A95E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5255E4-B4CD-EA4B-99DB-DEA4A7459533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22480" windowHeight="20420" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14320" yWindow="3220" windowWidth="22480" windowHeight="20420" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UTG" sheetId="1" r:id="rId1"/>
@@ -18915,6 +18915,52 @@
         <r>
           <rPr>
             <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Call
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000044000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Call
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000045000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -18925,7 +18971,53 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000044000000}">
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000046000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Call
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000047000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Raise
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Standard open based on position strength and hand playability</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000048000000}">
       <text>
         <r>
           <rPr>
@@ -18940,7 +19032,112 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000045000000}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000049000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Raise
+Cash: Standard open based on position strength and hand playability</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000050000000}">
       <text>
         <r>
           <rPr>
@@ -18955,7 +19152,511 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000046000000}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000051000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Call
+Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000052000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Call
+Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000053000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000054000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Call
+Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000055000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Raise
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Standard open based on position strength and hand playability</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000056000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000057000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000058000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000059000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Call
+Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000060000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000061000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000062000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000063000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Raise
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Standard open based on position strength and hand playability</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000064000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000065000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000066000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Fold
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000067000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000068000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000069000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Call
+Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000070000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000071000000}">
       <text>
         <r>
           <rPr>
@@ -18978,30 +19679,67 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000047000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Recommended: Raise
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>Cash: Standard open based on position strength and hand playability</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000048000000}">
+    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000072000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000073000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000074000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000075000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000076000000}">
       <text>
         <r>
           <rPr>
@@ -19016,112 +19754,195 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000049000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00004F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Raise
-Cash: Standard open based on position strength and hand playability</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000050000000}">
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000077000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000078000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000079000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Recommended: Call
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash: Marginal hand – playable but not strong enough to raise</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000080000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000081000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000082000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000083000000}">
       <text>
         <r>
           <rPr>
@@ -19136,67 +19957,127 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000051000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000052000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000053000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000054000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000055000000}">
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000084000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000085000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000086000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000087000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000088000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000089000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00008A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00008B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Recommended: Fold
+Cash: Below opening threshold for this position</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00008C000000}">
       <text>
         <r>
           <rPr>
@@ -19205,7 +20086,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Recommended: Raise
+          <t xml:space="preserve">Recommended: Fold
 </t>
         </r>
         <r>
@@ -19215,856 +20096,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>Cash: Standard open based on position strength and hand playability</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000056000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000057000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000058000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000059000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00005F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000060000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000061000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000062000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000063000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Recommended: Raise
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>Cash: Standard open based on position strength and hand playability</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000064000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000065000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000066000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000067000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000068000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000069000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00006F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000070000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000071000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Recommended: Call
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000072000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000073000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000074000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000075000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000076000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000077000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000078000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000079000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00007F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Recommended: Call
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000080000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000081000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000082000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000083000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Call
-Cash: Marginal hand – playable but not strong enough to raise</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000084000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000085000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000086000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000087000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000088000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000089000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00008A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00008B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00008C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Recommended: Fold
-Cash: Below opening threshold for this position</t>
+          <t>Cash: Below opening threshold for this position</t>
         </r>
       </text>
     </comment>
@@ -23276,7 +23308,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -23296,21 +23328,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -23399,17 +23416,19 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -23421,19 +23440,17 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -23638,43 +23655,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -24335,43 +24352,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -25032,43 +25049,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -25729,43 +25746,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -26426,43 +26443,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -27123,43 +27140,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -27820,43 +27837,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -28517,43 +28534,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
@@ -28561,9 +28578,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="15" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -28609,14 +28626,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
@@ -28659,17 +28676,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="19" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="10" t="s">
@@ -28709,20 +28726,20 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="10" t="s">
@@ -28753,7 +28770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -28763,13 +28780,13 @@
       <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="16" t="s">
         <v>18</v>
       </c>
       <c r="G7" s="12" t="s">
@@ -28797,7 +28814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -28810,13 +28827,13 @@
       <c r="D8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="19" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H8" s="11" t="s">
@@ -28841,7 +28858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -28857,13 +28874,13 @@
       <c r="E9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="11" t="s">
@@ -28885,7 +28902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -28904,13 +28921,13 @@
       <c r="F10" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="20" t="s">
         <v>19</v>
       </c>
       <c r="H10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="18" t="s">
         <v>3</v>
       </c>
       <c r="J10" s="11" t="s">
@@ -28929,7 +28946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -28951,13 +28968,13 @@
       <c r="G11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="21" t="s">
         <v>3</v>
       </c>
       <c r="I11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="18" t="s">
         <v>3</v>
       </c>
       <c r="K11" s="11" t="s">
@@ -28973,7 +28990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -28998,13 +29015,13 @@
       <c r="H12" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="21" t="s">
         <v>3</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="K12" s="18" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="11" t="s">
@@ -29017,7 +29034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -29045,13 +29062,13 @@
       <c r="I13" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="21" t="s">
         <v>3</v>
       </c>
       <c r="K13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="18" t="s">
         <v>3</v>
       </c>
       <c r="M13" s="11" t="s">
@@ -29061,7 +29078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -29092,20 +29109,20 @@
       <c r="J14" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="21" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="18" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -29139,17 +29156,17 @@
       <c r="K15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="24" t="s">
+      <c r="L15" s="21" t="s">
         <v>3</v>
       </c>
       <c r="M15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="N15" s="21" t="s">
+      <c r="N15" s="18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -29186,7 +29203,7 @@
       <c r="L16" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="M16" s="24" t="s">
+      <c r="M16" s="21" t="s">
         <v>3</v>
       </c>
       <c r="N16" s="26" t="s">
@@ -29214,43 +29231,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
